--- a/languages.xlsx
+++ b/languages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannguyen/Desktop/Tasks/Python/depp/Predict_WC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBA4222-CDF3-7D4E-8463-3E6BB8145C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8A34F9-F125-C94F-B4E7-1D09878BDB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="1100" windowWidth="28040" windowHeight="17440" xr2:uid="{4C45AC29-E9E1-5145-AB1D-B379358BFAF1}"/>
   </bookViews>
@@ -152,22 +152,6 @@
     <t>Check Line up </t>
   </si>
   <si>
-    <r>
-      <t>Simulating Probability</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>We generate the possibility of being World Cup champion for each participant by simulating events using probability. Choose the year of the World Cup and how many times you want to simulate it! </t>
-  </si>
-  <si>
     <t>Start Simulating! </t>
   </si>
   <si>
@@ -244,6 +228,25 @@
   </si>
   <si>
     <t xml:space="preserve">Full World Cup 2022 Predicting </t>
+  </si>
+  <si>
+    <r>
+      <t>Simulating Probability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> by Monte-carlo method</t>
+    </r>
+  </si>
+  <si>
+    <t>We generate the possibility of participating in round of 16, quarter-final, semi-final, final and being champion for each team based on selected ML model and Monte-carlo simulation. Monte-carlo simulation iterates a process with random factors to obtain possible events. 
+You can find more about Monte-carlo method by this wikipedia link:
+https://en.wikipedia.org/wiki/Monte_Carlo_method
+When we have the ML models ready, we can start simulating the possible events by changing random factor in amount of times, and count how many times a team makes themself to group of 16 until being champion.</t>
   </si>
 </sst>
 </file>
@@ -324,8 +327,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,24 +648,24 @@
   <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="72.6640625" customWidth="1"/>
+    <col min="1" max="1" width="170.33203125" customWidth="1"/>
     <col min="2" max="2" width="74.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -697,10 +702,10 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -761,10 +766,10 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -828,7 +833,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -836,7 +841,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -844,47 +849,47 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="121" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>49</v>
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/languages.xlsx
+++ b/languages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannguyen/Desktop/Tasks/Python/depp/Predict_WC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8A34F9-F125-C94F-B4E7-1D09878BDB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAC03A0-D00F-8D4A-A060-D669E23E7C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="1100" windowWidth="28040" windowHeight="17440" xr2:uid="{4C45AC29-E9E1-5145-AB1D-B379358BFAF1}"/>
   </bookViews>
@@ -246,7 +246,8 @@
     <t>We generate the possibility of participating in round of 16, quarter-final, semi-final, final and being champion for each team based on selected ML model and Monte-carlo simulation. Monte-carlo simulation iterates a process with random factors to obtain possible events. 
 You can find more about Monte-carlo method by this wikipedia link:
 https://en.wikipedia.org/wiki/Monte_Carlo_method
-When we have the ML models ready, we can start simulating the possible events by changing random factor in amount of times, and count how many times a team makes themself to group of 16 until being champion.</t>
+When we have the ML models ready, we can start simulating the possible events by changing random factor in amount of times, and count how many times a team makes themself to group of 16 until being champion.
+Due to complicated processing, we limit the number of time simulating to 1000.</t>
   </si>
 </sst>
 </file>
@@ -860,7 +861,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="121" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" ht="151" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>58</v>
       </c>

--- a/languages.xlsx
+++ b/languages.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannguyen/Desktop/Tasks/Python/depp/Predict_WC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAC03A0-D00F-8D4A-A060-D669E23E7C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1AA3DB-0ED1-E244-9D05-7321610390F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="1100" windowWidth="28040" windowHeight="17440" xr2:uid="{4C45AC29-E9E1-5145-AB1D-B379358BFAF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="87">
   <si>
     <t>Please select algorithm</t>
   </si>
@@ -249,12 +249,156 @@
 When we have the ML models ready, we can start simulating the possible events by changing random factor in amount of times, and count how many times a team makes themself to group of 16 until being champion.
 Due to complicated processing, we limit the number of time simulating to 1000.</t>
   </si>
+  <si>
+    <t>Arabic</t>
+  </si>
+  <si>
+    <r>
+      <t>أداة التوقع بكأس العالم لكرة القدم 2022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>يرجى اختيار الخوارزمية </t>
+  </si>
+  <si>
+    <t>الانحدار اللوجستي</t>
+  </si>
+  <si>
+    <t>الغابة العشوائية </t>
+  </si>
+  <si>
+    <r>
+      <t>توقع كامل لكأس العالم 2022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>ابدأ في التوقع باستخدام الخوارزمية المحددة من دور المجموعات حتى المباراة النهائية </t>
+  </si>
+  <si>
+    <t>ابدأ التوقع! </t>
+  </si>
+  <si>
+    <r>
+      <t>توقع بين فريقين</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>حدد الفريق 1 </t>
+  </si>
+  <si>
+    <t>حدد الفريق 2 </t>
+  </si>
+  <si>
+    <t>توقع! </t>
+  </si>
+  <si>
+    <r>
+      <t>اختر أفضل 16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>المجموعة أ </t>
+  </si>
+  <si>
+    <t>المجموعة ب </t>
+  </si>
+  <si>
+    <t>المجموعة ج </t>
+  </si>
+  <si>
+    <t>المجموعة د </t>
+  </si>
+  <si>
+    <t>المجموعة هـ </t>
+  </si>
+  <si>
+    <t>المجموعة و </t>
+  </si>
+  <si>
+    <t>المجموعة ز </t>
+  </si>
+  <si>
+    <t>المجموعة ح</t>
+  </si>
+  <si>
+    <t>اختر أحد الخيارات </t>
+  </si>
+  <si>
+    <t>تحقق من الترتيب </t>
+  </si>
+  <si>
+    <r>
+      <t>محاكاة الاحتمالات</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>نولد إمكانية أن يصبح كل مشارك بطلا لكأس العالم من خلال محاكاة الأحداث باستخدام الاحتمالات. اختر سنة كأس العالم وكم مرة تريد محاكاتها! </t>
+  </si>
+  <si>
+    <t>ابدأ المحاكاة! </t>
+  </si>
+  <si>
+    <t>اختر السنة </t>
+  </si>
+  <si>
+    <t>كم مرة تريد أن تحاكي؟ </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -299,6 +443,34 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF262730"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -320,7 +492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -331,6 +503,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -646,251 +836,342 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC7FD2E-B823-EF49-98C1-F03F0502ED40}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="170.33203125" customWidth="1"/>
+    <col min="1" max="1" width="59.5" customWidth="1"/>
     <col min="2" max="2" width="74.33203125" customWidth="1"/>
+    <col min="3" max="3" width="56.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>51</v>
       </c>
       <c r="B1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C2" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C3" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C4" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C5" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C6" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>56</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C7" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C8" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C9" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C10" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C11" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C12" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C13" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C14" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C15" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C16" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C21" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C23" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C24" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C25" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="151" x14ac:dyDescent="0.2">
+      <c r="C26" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="241" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C27" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C28" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C29" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>47</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/languages.xlsx
+++ b/languages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannguyen/Desktop/Tasks/Python/depp/Predict_WC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1AA3DB-0ED1-E244-9D05-7321610390F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE8B118-A7A5-8540-8C1E-DA63EED4085A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="1100" windowWidth="28040" windowHeight="17440" xr2:uid="{4C45AC29-E9E1-5145-AB1D-B379358BFAF1}"/>
   </bookViews>
@@ -243,13 +243,6 @@
     </r>
   </si>
   <si>
-    <t>We generate the possibility of participating in round of 16, quarter-final, semi-final, final and being champion for each team based on selected ML model and Monte-carlo simulation. Monte-carlo simulation iterates a process with random factors to obtain possible events. 
-You can find more about Monte-carlo method by this wikipedia link:
-https://en.wikipedia.org/wiki/Monte_Carlo_method
-When we have the ML models ready, we can start simulating the possible events by changing random factor in amount of times, and count how many times a team makes themself to group of 16 until being champion.
-Due to complicated processing, we limit the number of time simulating to 1000.</t>
-  </si>
-  <si>
     <t>Arabic</t>
   </si>
   <si>
@@ -392,6 +385,12 @@
   </si>
   <si>
     <t>كم مرة تريد أن تحاكي؟ </t>
+  </si>
+  <si>
+    <t>We generate the possibility of participating in round of 16, quarter-final, semi-final, final and being champion for each team based on selected ML model and Monte-carlo simulation. Monte-carlo simulation iterates a process with random factors to obtain possible events. 
+You can find more about Monte-carlo method by this wikipedia link:
+https://en.wikipedia.org/wiki/Monte_Carlo_method
+When we have the ML models ready, we can start simulating the possible events by changing random factor in amount of times, and count how many times a team makes themself to group of 16 until being champion.</t>
   </si>
 </sst>
 </file>
@@ -852,7 +851,7 @@
         <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -863,7 +862,7 @@
         <v>53</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -874,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -885,7 +884,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -896,7 +895,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -918,10 +917,10 @@
         <v>55</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -929,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -940,7 +939,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -951,7 +950,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -962,7 +961,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -973,7 +972,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -984,7 +983,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -995,7 +994,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1006,7 +1005,7 @@
         <v>49</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1017,7 +1016,7 @@
         <v>27</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1028,7 +1027,7 @@
         <v>26</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1039,7 +1038,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1050,7 +1049,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1061,7 +1060,7 @@
         <v>23</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1072,7 +1071,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1083,7 +1082,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1094,7 +1093,7 @@
         <v>41</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1105,7 +1104,7 @@
         <v>42</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1116,7 +1115,7 @@
         <v>52</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1127,18 +1126,18 @@
         <v>43</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="241" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="196" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1149,7 +1148,7 @@
         <v>45</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1160,7 +1159,7 @@
         <v>46</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1171,7 +1170,7 @@
         <v>47</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/languages.xlsx
+++ b/languages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannguyen/Desktop/Tasks/Python/depp/Predict_WC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE8B118-A7A5-8540-8C1E-DA63EED4085A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7BFC4B-2A6B-134C-BE18-710E3FF34C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="1100" windowWidth="28040" windowHeight="17440" xr2:uid="{4C45AC29-E9E1-5145-AB1D-B379358BFAF1}"/>
   </bookViews>
@@ -180,9 +180,6 @@
     </r>
   </si>
   <si>
-    <t>Chúng tôi tính toán khả năng mỗi quốc gia tham dự có thể trở giành chiến thắng tại đấu trường World Cup bằng cách áp dụng các biến cố mô phỏng xác suất. Hãy chọn năm diễn ra World Cup mà bạn hứng thú và số lần mô phỏng mà bạn muốn! </t>
-  </si>
-  <si>
     <t>Bắt đầu mô phỏng! </t>
   </si>
   <si>
@@ -375,9 +372,6 @@
     </r>
   </si>
   <si>
-    <t>نولد إمكانية أن يصبح كل مشارك بطلا لكأس العالم من خلال محاكاة الأحداث باستخدام الاحتمالات. اختر سنة كأس العالم وكم مرة تريد محاكاتها! </t>
-  </si>
-  <si>
     <t>ابدأ المحاكاة! </t>
   </si>
   <si>
@@ -391,6 +385,18 @@
 You can find more about Monte-carlo method by this wikipedia link:
 https://en.wikipedia.org/wiki/Monte_Carlo_method
 When we have the ML models ready, we can start simulating the possible events by changing random factor in amount of times, and count how many times a team makes themself to group of 16 until being champion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> البطولة بناء على نموذج التعلم الآلي المختار ومحاكاة مونت كارلو. تكرر محاكاة مونت كارلو عملية بعوامل عشوائية للحصول على الأحداث المحتملة.
+يمكنك التعرف أكثر على طريقة مونت كارلو من خلال رابط ويكيبيديا هذا: https://ar.wikipedia.org/wiki/طريقة_مونت_كارلو
+عندما تجهز نماذج التعلم الآلي ، يمكننا البدء في محاكاة الأحداث المحتملة عن طريق تغيير عامل عشوائي في عدد المرات ، وإحصاء عدد المرات التي يصل فيها الفريق الى مجموعة الـ 16 حتى يتحصل على البطولة.
+كم مرة تريد استخدام المحاكاة؟</t>
+  </si>
+  <si>
+    <t>Chúng tôi tính toán khả năng tham dự vòng 16, tứ kết, bán kết, chung kết và trở thành nhà vô địch cho mỗi đội dựa trên mô hình ML đã chọn và mô phỏng Monte-carlo. Mô phỏng Monte-carlo lặp lại một quá trình với các yếu tố ngẫu nhiên để thu được các sự kiện có thể xảy ra.
+Bạn có thể tìm thêm về phương pháp Monte-carlo theo liên kết wikipedia này:
+https://en.wikipedia.org/wiki/Monte_Carlo_method
+Khi có sẵn các mô hình ML, chúng tôi có thể bắt đầu mô phỏng các sự kiện có thể xảy ra bằng cách thay đổi hệ số ngẫu nhiên trong khoảng thời gian và đếm số lần một đội tự xếp mình vào nhóm 16 cho đến khi vô địch.</t>
   </si>
 </sst>
 </file>
@@ -491,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -520,6 +526,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -845,24 +854,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -873,7 +882,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -884,7 +893,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -895,7 +904,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -911,13 +920,13 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -928,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -939,7 +948,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -950,7 +959,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -961,7 +970,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -972,7 +981,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -983,7 +992,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -994,18 +1003,18 @@
         <v>20</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1016,7 +1025,7 @@
         <v>27</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1027,7 +1036,7 @@
         <v>26</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1038,7 +1047,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1049,7 +1058,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1060,7 +1069,7 @@
         <v>23</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1071,7 +1080,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1082,7 +1091,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1093,7 +1102,7 @@
         <v>41</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1104,7 +1113,7 @@
         <v>42</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1112,32 +1121,32 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="196" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="289" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="C27" s="12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1145,10 +1154,10 @@
         <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1156,10 +1165,10 @@
         <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1167,10 +1176,10 @@
         <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
